--- a/artfynd/A 50496-2021 artfynd.xlsx
+++ b/artfynd/A 50496-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50496-2021 artfynd.xlsx
+++ b/artfynd/A 50496-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58531967</v>
+        <v>68489017</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +709,17 @@
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björsäter sn, Björksveden, 300m ONO, Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562132.3857452531</v>
+        <v>562138</v>
       </c>
       <c r="R2" t="n">
-        <v>6465477.35443949</v>
+        <v>6465495</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,27 +763,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Göransson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Göransson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68489017</v>
+        <v>68489006</v>
       </c>
       <c r="B3" t="n">
-        <v>94112</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,37 +786,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562137.8998855111</v>
+        <v>562186</v>
       </c>
       <c r="R3" t="n">
-        <v>6465494.775184963</v>
+        <v>6465483</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,27 +849,18 @@
           <t>2017-10-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,12 +882,7 @@
         <v>68489000</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562293.7071443351</v>
+        <v>562294</v>
       </c>
       <c r="R4" t="n">
-        <v>6465525.598179745</v>
+        <v>6465526</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,19 +953,9 @@
           <t>2017-10-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68489006</v>
+        <v>96257041</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,40 +994,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562185.9665992435</v>
+        <v>562169</v>
       </c>
       <c r="R5" t="n">
-        <v>6465483.451867687</v>
+        <v>6465548</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,22 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96257041</v>
+        <v>58531967</v>
       </c>
       <c r="B6" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,44 +1099,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5741</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Björsäter sn, Björksveden, 300m ONO, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562169.1563913315</v>
+        <v>562132</v>
       </c>
       <c r="R6" t="n">
-        <v>6465548.319531723</v>
+        <v>6465477</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,22 +1156,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,19 +1170,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Andreas Göransson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Andreas Göransson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50496-2021 artfynd.xlsx
+++ b/artfynd/A 50496-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68489017</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68489006</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68489000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96257041</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,8 +1210,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58531967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>